--- a/reps.xlsx
+++ b/reps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b5bd79253e10ed0a/바탕 화면/스트라우만/주문시스템/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC71EB6B-5638-4653-99EA-CD7E1B73498E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{BC71EB6B-5638-4653-99EA-CD7E1B73498E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE75A199-EB11-4C97-AD10-4EBD5A36D197}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDC0E029-99CA-40FE-8171-AC9956E0BB70}"/>
+    <workbookView xWindow="795" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{EDC0E029-99CA-40FE-8171-AC9956E0BB70}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>코드</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,6 +78,14 @@
   </si>
   <si>
     <t>김수미 차장</t>
+  </si>
+  <si>
+    <t>K58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김현수 팀장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -477,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1C4161-CE65-4012-ADA3-ACBA876F61BC}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
@@ -550,6 +558,17 @@
         <v>8342102671</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1">
+        <v>810407231</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
